--- a/tools/i18n/FrameworkI18n.xlsx
+++ b/tools/i18n/FrameworkI18n.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11775"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,213 +27,231 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="76">
   <si>
     <t>key</t>
   </si>
   <si>
+    <t>zh-cn</t>
+  </si>
+  <si>
     <t>en-us</t>
   </si>
   <si>
-    <t>zh-cn</t>
-  </si>
-  <si>
     <t>NET_ERROR_1</t>
   </si>
   <si>
+    <t>网络错误</t>
+  </si>
+  <si>
     <t>Network error</t>
   </si>
   <si>
-    <t>网络错误</t>
-  </si>
-  <si>
     <t>NET_ERROR_2</t>
   </si>
   <si>
+    <t>网络连接异常，请检查网络</t>
+  </si>
+  <si>
     <t>Network connection error, please check your network</t>
   </si>
   <si>
-    <t>网络连接异常，请检查网络</t>
-  </si>
-  <si>
     <t>NET_ERROR_3</t>
   </si>
   <si>
-    <t>Disconnected</t>
-  </si>
-  <si>
-    <t>已断开连接</t>
+    <t>网络不稳定(%{latency}ms)</t>
+  </si>
+  <si>
+    <t>Unstable Network(%{latency}ms)</t>
   </si>
   <si>
     <t>NET_ERROR_4</t>
   </si>
   <si>
-    <t>You have been disconnected from the server due to timeout</t>
-  </si>
-  <si>
-    <t>由于超时，您已与服务器断开连接</t>
+    <t>网络连接断开</t>
+  </si>
+  <si>
+    <t>Network Disconnected</t>
   </si>
   <si>
     <t>NET_ERROR_5</t>
   </si>
   <si>
-    <t>Reconnect</t>
-  </si>
-  <si>
-    <t>重新连接</t>
+    <t>心跳超时，尝试重连...</t>
+  </si>
+  <si>
+    <t>Heartbeat timeout, attempting reconnection...</t>
   </si>
   <si>
     <t>NET_ERROR_6</t>
   </si>
   <si>
-    <t>Connection lost (Error code: %{code})</t>
-  </si>
-  <si>
-    <t>连接已断开（错误码：%{code}）</t>
+    <t>正在重新连接...</t>
+  </si>
+  <si>
+    <t>Reconnecting...</t>
   </si>
   <si>
     <t>NET_ERROR_7</t>
   </si>
   <si>
+    <t>与服务器连接中断</t>
+  </si>
+  <si>
+    <t>Connection to server lost</t>
+  </si>
+  <si>
+    <t>NET_ERROR_8</t>
+  </si>
+  <si>
+    <t>与服务器断开了连接，请重新登录</t>
+  </si>
+  <si>
+    <t>Disconnected from server, please log in again</t>
+  </si>
+  <si>
+    <t>NET_ERROR_9</t>
+  </si>
+  <si>
+    <t>重连成功</t>
+  </si>
+  <si>
     <t>Reconnection successful</t>
   </si>
   <si>
-    <t>重连成功</t>
-  </si>
-  <si>
-    <t>NET_ERROR_8</t>
+    <t>NET_ERROR_10</t>
+  </si>
+  <si>
+    <t>重连失败</t>
   </si>
   <si>
     <t>Reconnection failed</t>
   </si>
   <si>
-    <t>重连失败</t>
-  </si>
-  <si>
     <t>ERROR_100</t>
   </si>
   <si>
+    <t>用户未登录</t>
+  </si>
+  <si>
     <t>User not logged in</t>
   </si>
   <si>
-    <t>用户未登录</t>
-  </si>
-  <si>
     <t>ERROR_101</t>
   </si>
   <si>
+    <t>用户被停用</t>
+  </si>
+  <si>
     <t>User disabled</t>
   </si>
   <si>
-    <t>用户被停用</t>
-  </si>
-  <si>
     <t>ERROR_102</t>
   </si>
   <si>
+    <t>用户注销</t>
+  </si>
+  <si>
     <t>User account deactivated</t>
   </si>
   <si>
-    <t>用户注销</t>
-  </si>
-  <si>
     <t>ERROR_300</t>
   </si>
   <si>
+    <t>参数错误</t>
+  </si>
+  <si>
     <t>Parameter error</t>
   </si>
   <si>
-    <t>参数错误</t>
-  </si>
-  <si>
     <t>ERROR_301</t>
   </si>
   <si>
+    <t>服务器异常</t>
+  </si>
+  <si>
     <t>Server error</t>
   </si>
   <si>
-    <t>服务器异常</t>
-  </si>
-  <si>
     <t>ERROR_302</t>
   </si>
   <si>
+    <t>货币不足</t>
+  </si>
+  <si>
     <t>Insufficient currency</t>
   </si>
   <si>
-    <t>货币不足</t>
-  </si>
-  <si>
     <t>ERROR_303</t>
   </si>
   <si>
+    <t>配置不存在</t>
+  </si>
+  <si>
     <t>Configuration not found</t>
   </si>
   <si>
-    <t>配置不存在</t>
-  </si>
-  <si>
     <t>ERROR_304</t>
   </si>
   <si>
+    <t>任务不存在</t>
+  </si>
+  <si>
     <t>Task not found</t>
   </si>
   <si>
-    <t>任务不存在</t>
-  </si>
-  <si>
     <t>ERROR_305</t>
   </si>
   <si>
+    <t>奖励已领取</t>
+  </si>
+  <si>
     <t>Reward already claimed</t>
   </si>
   <si>
-    <t>奖励已领取</t>
-  </si>
-  <si>
     <t>SYSTEM_1</t>
   </si>
   <si>
+    <t>确认</t>
+  </si>
+  <si>
     <t>confirm</t>
   </si>
   <si>
-    <t>确认</t>
-  </si>
-  <si>
     <t>SYSTEM_2</t>
   </si>
   <si>
+    <t>取消</t>
+  </si>
+  <si>
     <t>cancel</t>
   </si>
   <si>
-    <t>取消</t>
-  </si>
-  <si>
     <t>SYSTEM_3</t>
   </si>
   <si>
+    <t>检测到您仍在房间中</t>
+  </si>
+  <si>
     <t>We have detected that you are still in the room</t>
   </si>
   <si>
-    <t>检测到您仍在房间中</t>
-  </si>
-  <si>
     <t>SYSTEM_4</t>
   </si>
   <si>
+    <t>超时</t>
+  </si>
+  <si>
     <t>TIME OUT</t>
   </si>
   <si>
-    <t>超时</t>
-  </si>
-  <si>
     <t>SYSTEM_5</t>
   </si>
   <si>
+    <t>连续两次超时，请休息一下。</t>
+  </si>
+  <si>
     <t>Two consecutive timeouts, let's take a break.</t>
-  </si>
-  <si>
-    <t>连续两次超时，请休息一下。</t>
   </si>
   <si>
     <t>SYSTEM_6</t>
@@ -249,7 +267,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -261,6 +279,12 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -726,170 +750,174 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1273,525 +1301,500 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F70"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
+  <dimension ref="A1:E72"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="26.5" style="1" customWidth="1"/>
-    <col min="2" max="3" width="47.825" style="2" customWidth="1"/>
+    <col min="2" max="2" width="47.825" style="2" customWidth="1"/>
+    <col min="3" max="3" width="93.15" style="2" customWidth="1"/>
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:5">
+      <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-    </row>
-    <row r="3" ht="28.5" spans="1:6">
-      <c r="A3" s="3" t="s">
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+    </row>
+    <row r="3" ht="20" customHeight="1" spans="1:5">
+      <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="3" t="s">
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-    </row>
-    <row r="5" ht="28.5" spans="1:6">
-      <c r="A5" s="3" t="s">
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" ht="15" spans="1:5">
+      <c r="A7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="3" t="s">
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="3" t="s">
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="3" t="s">
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="3" t="s">
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="3" t="s">
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="3" t="s">
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="3" t="s">
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="3" t="s">
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-    </row>
-    <row r="25" s="1" customFormat="1" spans="1:6">
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="B29" s="6"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-    </row>
-    <row r="33" spans="2:5">
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-    </row>
-    <row r="34" spans="2:5">
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-    </row>
-    <row r="35" spans="2:5">
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-    </row>
-    <row r="36" spans="2:5">
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-    </row>
-    <row r="37" spans="2:5">
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-    </row>
-    <row r="38" spans="2:5">
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-    </row>
-    <row r="39" spans="2:5">
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-    </row>
-    <row r="40" spans="2:5">
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-    </row>
-    <row r="41" spans="2:5">
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-    </row>
-    <row r="42" spans="2:5">
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-    </row>
-    <row r="43" spans="2:5">
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-    </row>
-    <row r="44" spans="2:5">
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-    </row>
-    <row r="45" spans="2:5">
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
-    </row>
-    <row r="46" spans="2:5">
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
-    </row>
-    <row r="47" spans="2:5">
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="4"/>
-    </row>
-    <row r="48" spans="2:5">
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
-    </row>
-    <row r="49" spans="3:5">
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
-    </row>
-    <row r="50" spans="3:5">
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
-    </row>
-    <row r="51" spans="3:5">
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-    </row>
-    <row r="52" spans="3:5">
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
-    </row>
-    <row r="53" spans="3:5">
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
-    </row>
-    <row r="54" spans="3:5">
-      <c r="C54" s="4"/>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
-    </row>
-    <row r="55" spans="3:5">
-      <c r="C55" s="4"/>
-      <c r="D55" s="4"/>
-      <c r="E55" s="4"/>
-    </row>
-    <row r="56" spans="3:5">
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-    </row>
-    <row r="65" s="1" customFormat="1" spans="2:3">
-      <c r="B65" s="2"/>
-      <c r="C65" s="2"/>
-    </row>
-    <row r="68" spans="2:3">
-      <c r="B68" s="7"/>
-      <c r="C68" s="7"/>
-    </row>
-    <row r="69" spans="2:3">
-      <c r="B69" s="7"/>
-      <c r="C69" s="7"/>
+      <c r="B24" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="1:5">
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="B30" s="7"/>
+      <c r="D30" s="7"/>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="B31" s="8"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="8"/>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+    </row>
+    <row r="33" spans="2:4">
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+    </row>
+    <row r="34" spans="2:4">
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+    </row>
+    <row r="35" spans="2:4">
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+    </row>
+    <row r="36" spans="2:4">
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+    </row>
+    <row r="37" spans="2:4">
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+    </row>
+    <row r="38" spans="2:4">
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+    </row>
+    <row r="39" spans="2:4">
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+    </row>
+    <row r="40" spans="2:4">
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+    </row>
+    <row r="41" spans="2:4">
+      <c r="B41" s="8"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+    </row>
+    <row r="42" spans="2:4">
+      <c r="B42" s="8"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="8"/>
+    </row>
+    <row r="43" spans="2:4">
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="8"/>
+    </row>
+    <row r="44" spans="2:4">
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+    </row>
+    <row r="45" spans="2:4">
+      <c r="B45" s="8"/>
+      <c r="D45" s="8"/>
+    </row>
+    <row r="46" spans="2:4">
+      <c r="B46" s="8"/>
+      <c r="D46" s="8"/>
+    </row>
+    <row r="47" spans="2:4">
+      <c r="B47" s="8"/>
+      <c r="D47" s="8"/>
+    </row>
+    <row r="48" spans="2:4">
+      <c r="B48" s="8"/>
+      <c r="D48" s="8"/>
+    </row>
+    <row r="49" spans="2:4">
+      <c r="B49" s="8"/>
+      <c r="D49" s="8"/>
+    </row>
+    <row r="50" spans="2:4">
+      <c r="B50" s="8"/>
+      <c r="D50" s="8"/>
+    </row>
+    <row r="51" spans="2:4">
+      <c r="B51" s="8"/>
+      <c r="D51" s="8"/>
+    </row>
+    <row r="52" spans="2:4">
+      <c r="B52" s="8"/>
+      <c r="D52" s="8"/>
+    </row>
+    <row r="53" spans="2:4">
+      <c r="B53" s="8"/>
+      <c r="D53" s="8"/>
+    </row>
+    <row r="54" spans="2:4">
+      <c r="B54" s="8"/>
+      <c r="D54" s="8"/>
+    </row>
+    <row r="55" spans="2:4">
+      <c r="B55" s="8"/>
+      <c r="D55" s="8"/>
+    </row>
+    <row r="56" spans="2:4">
+      <c r="B56" s="8"/>
+      <c r="D56" s="8"/>
+    </row>
+    <row r="57" spans="2:4">
+      <c r="B57" s="8"/>
+      <c r="D57" s="8"/>
+    </row>
+    <row r="58" spans="2:4">
+      <c r="B58" s="8"/>
+      <c r="D58" s="8"/>
+    </row>
+    <row r="67" s="1" customFormat="1" spans="2:3">
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
     </row>
     <row r="70" spans="2:3">
-      <c r="B70" s="7"/>
-      <c r="C70" s="7"/>
+      <c r="B70" s="9"/>
+      <c r="C70" s="9"/>
+    </row>
+    <row r="71" spans="2:3">
+      <c r="B71" s="9"/>
+      <c r="C71" s="9"/>
+    </row>
+    <row r="72" spans="2:3">
+      <c r="B72" s="9"/>
+      <c r="C72" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tools/i18n/FrameworkI18n.xlsx
+++ b/tools/i18n/FrameworkI18n.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="67">
   <si>
     <t>key</t>
   </si>
@@ -41,85 +41,58 @@
     <t>NET_ERROR_1</t>
   </si>
   <si>
-    <t>网络错误</t>
-  </si>
-  <si>
-    <t>Network error</t>
+    <t>网络连接断开，请重新登录</t>
+  </si>
+  <si>
+    <t>Network Disconnected, please log in again</t>
   </si>
   <si>
     <t>NET_ERROR_2</t>
   </si>
   <si>
+    <t>网络连接中断，尝试重连...</t>
+  </si>
+  <si>
+    <t>Network connection interrupted, attempting to reconnect...</t>
+  </si>
+  <si>
+    <t>NET_ERROR_3</t>
+  </si>
+  <si>
+    <t>网络不稳定(%{latency}ms)</t>
+  </si>
+  <si>
+    <t>Unstable Network(%{latency}ms)</t>
+  </si>
+  <si>
+    <t>NET_ERROR_4</t>
+  </si>
+  <si>
     <t>网络连接异常，请检查网络</t>
   </si>
   <si>
     <t>Network connection error, please check your network</t>
   </si>
   <si>
-    <t>NET_ERROR_3</t>
-  </si>
-  <si>
-    <t>网络不稳定(%{latency}ms)</t>
-  </si>
-  <si>
-    <t>Unstable Network(%{latency}ms)</t>
-  </si>
-  <si>
-    <t>NET_ERROR_4</t>
-  </si>
-  <si>
-    <t>网络连接断开</t>
-  </si>
-  <si>
-    <t>Network Disconnected</t>
-  </si>
-  <si>
     <t>NET_ERROR_5</t>
   </si>
   <si>
-    <t>心跳超时，尝试重连...</t>
-  </si>
-  <si>
-    <t>Heartbeat timeout, attempting reconnection...</t>
+    <t>正在重新连接...</t>
+  </si>
+  <si>
+    <t>Reconnecting...</t>
   </si>
   <si>
     <t>NET_ERROR_6</t>
   </si>
   <si>
-    <t>正在重新连接...</t>
-  </si>
-  <si>
-    <t>Reconnecting...</t>
+    <t>重连成功</t>
+  </si>
+  <si>
+    <t>Reconnection successful</t>
   </si>
   <si>
     <t>NET_ERROR_7</t>
-  </si>
-  <si>
-    <t>与服务器连接中断</t>
-  </si>
-  <si>
-    <t>Connection to server lost</t>
-  </si>
-  <si>
-    <t>NET_ERROR_8</t>
-  </si>
-  <si>
-    <t>与服务器断开了连接，请重新登录</t>
-  </si>
-  <si>
-    <t>Disconnected from server, please log in again</t>
-  </si>
-  <si>
-    <t>NET_ERROR_9</t>
-  </si>
-  <si>
-    <t>重连成功</t>
-  </si>
-  <si>
-    <t>Reconnection successful</t>
-  </si>
-  <si>
-    <t>NET_ERROR_10</t>
   </si>
   <si>
     <t>重连失败</t>
@@ -1301,7 +1274,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:E72"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="26.5" style="1" customWidth="1"/>
@@ -1325,10 +1298,10 @@
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="4"/>
@@ -1341,7 +1314,7 @@
       <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="4"/>
@@ -1373,24 +1346,24 @@
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" ht="15" spans="1:5">
       <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
     </row>
-    <row r="7" ht="15" spans="1:5">
+    <row r="7" spans="1:5">
       <c r="A7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>19</v>
       </c>
       <c r="C7" s="5" t="s">
@@ -1406,7 +1379,7 @@
       <c r="B8" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D8" s="4"/>
@@ -1416,10 +1389,10 @@
       <c r="A9" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="5" t="s">
         <v>26</v>
       </c>
       <c r="D9" s="4"/>
@@ -1442,7 +1415,7 @@
       <c r="A11" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C11" s="5" t="s">
@@ -1481,7 +1454,7 @@
       <c r="A14" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>40</v>
       </c>
       <c r="C14" s="5" t="s">
@@ -1599,64 +1572,40 @@
         <v>66</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-    </row>
-    <row r="27" s="1" customFormat="1" spans="1:5">
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
+    <row r="24" s="1" customFormat="1" spans="1:5">
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="B27" s="7"/>
+      <c r="D27" s="7"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="B28" s="8"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="8"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
     </row>
     <row r="30" spans="1:5">
-      <c r="B30" s="7"/>
-      <c r="D30" s="7"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
     </row>
     <row r="31" spans="1:5">
       <c r="B31" s="8"/>
-      <c r="C31" s="7"/>
+      <c r="C31" s="8"/>
       <c r="D31" s="8"/>
     </row>
     <row r="32" spans="1:5">
@@ -1711,17 +1660,14 @@
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="8"/>
-      <c r="C42" s="8"/>
       <c r="D42" s="8"/>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
       <c r="D43" s="8"/>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="8"/>
-      <c r="C44" s="8"/>
       <c r="D44" s="8"/>
     </row>
     <row r="45" spans="2:4">
@@ -1768,33 +1714,21 @@
       <c r="B55" s="8"/>
       <c r="D55" s="8"/>
     </row>
-    <row r="56" spans="2:4">
-      <c r="B56" s="8"/>
-      <c r="D56" s="8"/>
-    </row>
-    <row r="57" spans="2:4">
-      <c r="B57" s="8"/>
-      <c r="D57" s="8"/>
-    </row>
-    <row r="58" spans="2:4">
-      <c r="B58" s="8"/>
-      <c r="D58" s="8"/>
-    </row>
-    <row r="67" s="1" customFormat="1" spans="2:3">
-      <c r="B67" s="2"/>
-      <c r="C67" s="2"/>
-    </row>
-    <row r="70" spans="2:3">
-      <c r="B70" s="9"/>
-      <c r="C70" s="9"/>
-    </row>
-    <row r="71" spans="2:3">
-      <c r="B71" s="9"/>
-      <c r="C71" s="9"/>
-    </row>
-    <row r="72" spans="2:3">
-      <c r="B72" s="9"/>
-      <c r="C72" s="9"/>
+    <row r="64" s="1" customFormat="1" spans="2:4">
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+    </row>
+    <row r="67" spans="2:3">
+      <c r="B67" s="9"/>
+      <c r="C67" s="9"/>
+    </row>
+    <row r="68" spans="2:3">
+      <c r="B68" s="9"/>
+      <c r="C68" s="9"/>
+    </row>
+    <row r="69" spans="2:3">
+      <c r="B69" s="9"/>
+      <c r="C69" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tools/i18n/FrameworkI18n.xlsx
+++ b/tools/i18n/FrameworkI18n.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\ThirteenTexas\assets\framework\tools\i18n\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
@@ -149,10 +154,10 @@
     <t>ERROR_302</t>
   </si>
   <si>
-    <t>货币不足</t>
-  </si>
-  <si>
-    <t>Insufficient currency</t>
+    <t>筹码不足</t>
+  </si>
+  <si>
+    <t>Insufficient chips</t>
   </si>
   <si>
     <t>ERROR_303</t>

--- a/tools/i18n/FrameworkI18n.xlsx
+++ b/tools/i18n/FrameworkI18n.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
   <si>
     <t>key</t>
   </si>
@@ -232,7 +232,103 @@
     <t>Two consecutive timeouts, let's take a break.</t>
   </si>
   <si>
-    <t>SYSTEM_6</t>
+    <t>LOGIN_APPLE</t>
+  </si>
+  <si>
+    <t>通过 Apple 登录</t>
+  </si>
+  <si>
+    <t>Sign in with Apple</t>
+  </si>
+  <si>
+    <t>LOGIN_PHONE</t>
+  </si>
+  <si>
+    <t>手机登录</t>
+  </si>
+  <si>
+    <t>Sign in with Phone</t>
+  </si>
+  <si>
+    <t>LOGIN_WECHAT</t>
+  </si>
+  <si>
+    <t>微信登录</t>
+  </si>
+  <si>
+    <t>Sign in with WeChat</t>
+  </si>
+  <si>
+    <t>LOGIN_GUEST</t>
+  </si>
+  <si>
+    <t>游客登录</t>
+  </si>
+  <si>
+    <t>Guest Login</t>
+  </si>
+  <si>
+    <t>LOGIN_AGREEMENT_TIP</t>
+  </si>
+  <si>
+    <t>登录即表示您已阅读并同意</t>
+  </si>
+  <si>
+    <t>By logging in, you confirm you have read and agree to</t>
+  </si>
+  <si>
+    <t>AND</t>
+  </si>
+  <si>
+    <t>和</t>
+  </si>
+  <si>
+    <t>And</t>
+  </si>
+  <si>
+    <t>USER_AGREEMENT</t>
+  </si>
+  <si>
+    <t>用户协议</t>
+  </si>
+  <si>
+    <t>User Agreement</t>
+  </si>
+  <si>
+    <t>PRIVACY_POLICY</t>
+  </si>
+  <si>
+    <t>隐私政策</t>
+  </si>
+  <si>
+    <t>Privacy Policy</t>
+  </si>
+  <si>
+    <t>SERVICE_TERMS</t>
+  </si>
+  <si>
+    <t>服务条款</t>
+  </si>
+  <si>
+    <t>Terms of Service</t>
+  </si>
+  <si>
+    <t>HEALTHY_GAME_ADVICE_PART1</t>
+  </si>
+  <si>
+    <t>抵制不良游戏，拒绝盗版游戏。注意自我保护，谨防受骗上当。适度游戏益脑，沉迷游戏伤身。合理安排时间，享受健康生活。</t>
+  </si>
+  <si>
+    <t>Resist bad games, reject pirated games. Protect yourself and watch out for scams. Moderate gaming benefits your mind, while excessive gaming harms your health. Arrange your time wisely and enjoy a healthy life.</t>
+  </si>
+  <si>
+    <t>HEALTHY_GAME_ADVICE_PART2</t>
+  </si>
+  <si>
+    <t>批准文号:新厂出审[2017]4343号。出版物号:ISBN978-7-7979-7728-9 出版单位:福州169公司。</t>
+  </si>
+  <si>
+    <t>Approval Number: Xin Chang Chu Shen [2017] No. 4343 Publication Number: ISBN 978-7-7979-7728-9 Publisher: Fuzhou 169 Company</t>
   </si>
 </sst>
 </file>
@@ -255,23 +351,22 @@
     </font>
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Arial"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -873,24 +968,37 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1279,461 +1387,536 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="26.5" style="1" customWidth="1"/>
-    <col min="2" max="2" width="47.825" style="2" customWidth="1"/>
-    <col min="3" max="3" width="93.15" style="2" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="26.5" style="2" customWidth="1"/>
+    <col min="2" max="2" width="47.825" style="3" customWidth="1"/>
+    <col min="3" max="3" width="93.15" style="3" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="17.25" spans="1:5">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="4" t="s">
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+    </row>
+    <row r="2" ht="17.25" spans="1:5">
+      <c r="A2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:5">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="4" t="s">
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+    </row>
+    <row r="4" ht="17.25" spans="1:5">
+      <c r="A4" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="4" t="s">
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+    </row>
+    <row r="5" ht="17.25" spans="1:5">
+      <c r="A5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-    </row>
-    <row r="6" ht="15" spans="1:5">
-      <c r="A6" s="4" t="s">
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+    </row>
+    <row r="6" ht="17.25" spans="1:5">
+      <c r="A6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="4" t="s">
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+    </row>
+    <row r="7" ht="17.25" spans="1:5">
+      <c r="A7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="4" t="s">
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+    </row>
+    <row r="8" ht="17.25" spans="1:5">
+      <c r="A8" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="4" t="s">
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+    </row>
+    <row r="9" ht="17.25" spans="1:5">
+      <c r="A9" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="4" t="s">
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+    </row>
+    <row r="10" ht="17.25" spans="1:5">
+      <c r="A10" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="4" t="s">
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+    </row>
+    <row r="11" ht="17.25" spans="1:5">
+      <c r="A11" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="4" t="s">
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+    </row>
+    <row r="12" ht="17.25" spans="1:5">
+      <c r="A12" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="4" t="s">
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+    </row>
+    <row r="13" ht="17.25" spans="1:5">
+      <c r="A13" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="4" t="s">
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+    </row>
+    <row r="14" ht="17.25" spans="1:5">
+      <c r="A14" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="4" t="s">
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+    </row>
+    <row r="15" ht="17.25" spans="1:5">
+      <c r="A15" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="4" t="s">
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+    </row>
+    <row r="16" ht="17.25" spans="1:5">
+      <c r="A16" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="4" t="s">
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+    </row>
+    <row r="17" ht="17.25" spans="1:5">
+      <c r="A17" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="4" t="s">
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+    </row>
+    <row r="18" ht="17.25" spans="1:5">
+      <c r="A18" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="4" t="s">
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+    </row>
+    <row r="19" ht="17.25" spans="1:5">
+      <c r="A19" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="4" t="s">
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+    </row>
+    <row r="20" ht="17.25" spans="1:5">
+      <c r="A20" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="4" t="s">
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+    </row>
+    <row r="21" ht="17.25" spans="1:5">
+      <c r="A21" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="4" t="s">
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+    </row>
+    <row r="22" ht="17.25" spans="1:5">
+      <c r="A22" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="4" t="s">
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+    </row>
+    <row r="23" ht="18" spans="1:5">
+      <c r="A23" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="1:5">
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="B27" s="7"/>
-      <c r="D27" s="7"/>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="B28" s="8"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="8"/>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-    </row>
-    <row r="33" spans="2:4">
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-    </row>
-    <row r="34" spans="2:4">
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-    </row>
-    <row r="35" spans="2:4">
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-    </row>
-    <row r="36" spans="2:4">
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-    </row>
-    <row r="37" spans="2:4">
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-    </row>
-    <row r="38" spans="2:4">
-      <c r="B38" s="8"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-    </row>
-    <row r="39" spans="2:4">
-      <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-    </row>
-    <row r="40" spans="2:4">
-      <c r="B40" s="8"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
-    </row>
-    <row r="41" spans="2:4">
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-    </row>
-    <row r="42" spans="2:4">
-      <c r="B42" s="8"/>
-      <c r="D42" s="8"/>
-    </row>
-    <row r="43" spans="2:4">
-      <c r="B43" s="8"/>
-      <c r="D43" s="8"/>
-    </row>
-    <row r="44" spans="2:4">
-      <c r="B44" s="8"/>
-      <c r="D44" s="8"/>
-    </row>
-    <row r="45" spans="2:4">
-      <c r="B45" s="8"/>
-      <c r="D45" s="8"/>
-    </row>
-    <row r="46" spans="2:4">
-      <c r="B46" s="8"/>
-      <c r="D46" s="8"/>
-    </row>
-    <row r="47" spans="2:4">
-      <c r="B47" s="8"/>
-      <c r="D47" s="8"/>
-    </row>
-    <row r="48" spans="2:4">
-      <c r="B48" s="8"/>
-      <c r="D48" s="8"/>
+      <c r="B23" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" s="11"/>
+      <c r="E23" s="6"/>
+    </row>
+    <row r="24" ht="17.25" spans="1:5">
+      <c r="A24" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D24" s="12"/>
+      <c r="E24" s="6"/>
+    </row>
+    <row r="25" ht="17.25" spans="1:5">
+      <c r="A25" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D25" s="12"/>
+      <c r="E25" s="6"/>
+    </row>
+    <row r="26" ht="17.25" spans="1:5">
+      <c r="A26" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D26" s="12"/>
+      <c r="E26" s="6"/>
+    </row>
+    <row r="27" ht="17.25" spans="1:5">
+      <c r="A27" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D27" s="12"/>
+      <c r="E27" s="6"/>
+    </row>
+    <row r="28" customFormat="1" ht="17.25" spans="1:5">
+      <c r="A28" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D28" s="12"/>
+      <c r="E28" s="6"/>
+    </row>
+    <row r="29" s="1" customFormat="1" ht="17.25" spans="1:5">
+      <c r="A29" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" ht="17.25" spans="1:5">
+      <c r="A30" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" ht="17.25" spans="1:5">
+      <c r="A31" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" ht="51.75" spans="1:5">
+      <c r="A32" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+    </row>
+    <row r="33" ht="51.75" spans="1:5">
+      <c r="A33" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+    </row>
+    <row r="34" ht="17.25" spans="1:5">
+      <c r="A34" s="6"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="6"/>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="B37" s="13"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="B38" s="13"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="B39" s="13"/>
+      <c r="D39" s="13"/>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="B40" s="13"/>
+      <c r="D40" s="13"/>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="B41" s="13"/>
+      <c r="D41" s="13"/>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="B42" s="13"/>
+      <c r="D42" s="13"/>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="B43" s="13"/>
+      <c r="D43" s="13"/>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="B44" s="13"/>
+      <c r="D44" s="13"/>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="B45" s="13"/>
+      <c r="D45" s="13"/>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="B46" s="13"/>
+      <c r="D46" s="13"/>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="B47" s="13"/>
+      <c r="D47" s="13"/>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="B48" s="13"/>
+      <c r="D48" s="13"/>
     </row>
     <row r="49" spans="2:4">
-      <c r="B49" s="8"/>
-      <c r="D49" s="8"/>
+      <c r="B49" s="13"/>
+      <c r="D49" s="13"/>
     </row>
     <row r="50" spans="2:4">
-      <c r="B50" s="8"/>
-      <c r="D50" s="8"/>
+      <c r="B50" s="13"/>
+      <c r="D50" s="13"/>
     </row>
     <row r="51" spans="2:4">
-      <c r="B51" s="8"/>
-      <c r="D51" s="8"/>
+      <c r="B51" s="13"/>
+      <c r="D51" s="13"/>
     </row>
     <row r="52" spans="2:4">
-      <c r="B52" s="8"/>
-      <c r="D52" s="8"/>
-    </row>
-    <row r="53" spans="2:4">
-      <c r="B53" s="8"/>
-      <c r="D53" s="8"/>
-    </row>
-    <row r="54" spans="2:4">
-      <c r="B54" s="8"/>
-      <c r="D54" s="8"/>
-    </row>
-    <row r="55" spans="2:4">
-      <c r="B55" s="8"/>
-      <c r="D55" s="8"/>
-    </row>
-    <row r="64" s="1" customFormat="1" spans="2:4">
-      <c r="B64" s="2"/>
-      <c r="C64" s="2"/>
-    </row>
-    <row r="67" spans="2:3">
-      <c r="B67" s="9"/>
-      <c r="C67" s="9"/>
-    </row>
-    <row r="68" spans="2:3">
-      <c r="B68" s="9"/>
-      <c r="C68" s="9"/>
-    </row>
-    <row r="69" spans="2:3">
-      <c r="B69" s="9"/>
-      <c r="C69" s="9"/>
+      <c r="B52" s="13"/>
+      <c r="D52" s="13"/>
+    </row>
+    <row r="61" s="2" customFormat="1" spans="2:4">
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+    </row>
+    <row r="64" spans="2:4">
+      <c r="B64" s="14"/>
+      <c r="C64" s="14"/>
+    </row>
+    <row r="65" spans="2:3">
+      <c r="B65" s="14"/>
+      <c r="C65" s="14"/>
+    </row>
+    <row r="66" spans="2:3">
+      <c r="B66" s="14"/>
+      <c r="C66" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tools/i18n/FrameworkI18n.xlsx
+++ b/tools/i18n/FrameworkI18n.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
   <si>
     <t>key</t>
   </si>
@@ -185,6 +185,42 @@
   </si>
   <si>
     <t>Reward already claimed</t>
+  </si>
+  <si>
+    <t>ERROR_306</t>
+  </si>
+  <si>
+    <t>邮件不存在</t>
+  </si>
+  <si>
+    <t>Mail Does Not Exist</t>
+  </si>
+  <si>
+    <t>ERROR_307</t>
+  </si>
+  <si>
+    <t>邮件无奖励可领</t>
+  </si>
+  <si>
+    <t>No Rewards Available</t>
+  </si>
+  <si>
+    <t>ERROR_308</t>
+  </si>
+  <si>
+    <t>金币不足</t>
+  </si>
+  <si>
+    <t>Insufficient Gold</t>
+  </si>
+  <si>
+    <t>ERROR_309</t>
+  </si>
+  <si>
+    <t>钻石不足</t>
+  </si>
+  <si>
+    <t>Insufficient Diamonds</t>
   </si>
   <si>
     <t>SYSTEM_1</t>
@@ -968,7 +1004,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -979,9 +1015,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1387,7 +1420,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="26.5" style="2" customWidth="1"/>
@@ -1406,517 +1439,563 @@
       <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
     </row>
     <row r="2" ht="17.25" spans="1:5">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:5">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
     </row>
     <row r="4" ht="17.25" spans="1:5">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
     </row>
     <row r="5" ht="17.25" spans="1:5">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
     </row>
     <row r="6" ht="17.25" spans="1:5">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
     </row>
     <row r="7" ht="17.25" spans="1:5">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
     </row>
     <row r="8" ht="17.25" spans="1:5">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
     </row>
     <row r="9" ht="17.25" spans="1:5">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
     </row>
     <row r="10" ht="17.25" spans="1:5">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
     </row>
     <row r="11" ht="17.25" spans="1:5">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
     </row>
     <row r="12" ht="17.25" spans="1:5">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
     </row>
     <row r="13" ht="17.25" spans="1:5">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
     </row>
     <row r="14" ht="17.25" spans="1:5">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
     </row>
     <row r="15" ht="17.25" spans="1:5">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
     </row>
     <row r="16" ht="17.25" spans="1:5">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
     </row>
     <row r="17" ht="17.25" spans="1:5">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
     </row>
     <row r="18" ht="17.25" spans="1:5">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
     </row>
     <row r="19" ht="17.25" spans="1:5">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
     </row>
     <row r="20" ht="17.25" spans="1:5">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
     </row>
     <row r="21" ht="17.25" spans="1:5">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
     </row>
     <row r="22" ht="17.25" spans="1:5">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-    </row>
-    <row r="23" ht="18" spans="1:5">
-      <c r="A23" s="10" t="s">
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+    </row>
+    <row r="23" ht="17.25" spans="1:5">
+      <c r="A23" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="D23" s="11"/>
+      <c r="D23" s="6"/>
       <c r="E23" s="6"/>
     </row>
     <row r="24" ht="17.25" spans="1:5">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="D24" s="12"/>
+      <c r="D24" s="6"/>
       <c r="E24" s="6"/>
     </row>
     <row r="25" ht="17.25" spans="1:5">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="D25" s="12"/>
+      <c r="D25" s="6"/>
       <c r="E25" s="6"/>
     </row>
     <row r="26" ht="17.25" spans="1:5">
-      <c r="A26" s="10" t="s">
+      <c r="A26" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="D26" s="12"/>
+      <c r="D26" s="6"/>
       <c r="E26" s="6"/>
     </row>
-    <row r="27" ht="17.25" spans="1:5">
-      <c r="A27" s="10" t="s">
+    <row r="27" ht="18" spans="1:5">
+      <c r="A27" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="D27" s="12"/>
-      <c r="E27" s="6"/>
-    </row>
-    <row r="28" customFormat="1" ht="17.25" spans="1:5">
-      <c r="A28" s="10" t="s">
+      <c r="D27" s="10"/>
+      <c r="E27" s="4"/>
+    </row>
+    <row r="28" ht="17.25" spans="1:5">
+      <c r="A28" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="D28" s="12"/>
-      <c r="E28" s="6"/>
-    </row>
-    <row r="29" s="1" customFormat="1" ht="17.25" spans="1:5">
-      <c r="A29" s="10" t="s">
+      <c r="D28" s="11"/>
+      <c r="E28" s="4"/>
+    </row>
+    <row r="29" ht="17.25" spans="1:5">
+      <c r="A29" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="B29" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="9" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="30" s="1" customFormat="1" ht="17.25" spans="1:5">
-      <c r="A30" s="10" t="s">
+      <c r="D29" s="11"/>
+      <c r="E29" s="4"/>
+    </row>
+    <row r="30" ht="17.25" spans="1:5">
+      <c r="A30" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="B30" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="9" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="31" s="1" customFormat="1" ht="17.25" spans="1:5">
-      <c r="A31" s="10" t="s">
+      <c r="D30" s="11"/>
+      <c r="E30" s="4"/>
+    </row>
+    <row r="31" ht="17.25" spans="1:5">
+      <c r="A31" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C31" s="9" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="32" s="2" customFormat="1" ht="51.75" spans="1:5">
-      <c r="A32" s="10" t="s">
+      <c r="D31" s="11"/>
+      <c r="E31" s="4"/>
+    </row>
+    <row r="32" customFormat="1" ht="17.25" spans="1:5">
+      <c r="A32" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B32" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-    </row>
-    <row r="33" ht="51.75" spans="1:5">
-      <c r="A33" s="10" t="s">
+      <c r="D32" s="11"/>
+      <c r="E32" s="4"/>
+    </row>
+    <row r="33" s="1" customFormat="1" ht="17.25" spans="1:5">
+      <c r="A33" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="B33" s="10" t="s">
+      <c r="B33" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="C33" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-    </row>
-    <row r="34" ht="17.25" spans="1:5">
-      <c r="A34" s="6"/>
-      <c r="B34" s="12"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="6"/>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="B35" s="13"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="B36" s="13"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="B38" s="13"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
+    </row>
+    <row r="34" s="1" customFormat="1" ht="17.25" spans="1:5">
+      <c r="A34" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" ht="17.25" spans="1:5">
+      <c r="A35" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" ht="17.25" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D36" s="3"/>
+      <c r="E36" s="4"/>
+    </row>
+    <row r="37" ht="17.25" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D37" s="3"/>
+      <c r="E37" s="4"/>
+    </row>
+    <row r="38" ht="17.25" spans="1:5">
+      <c r="A38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="4"/>
     </row>
     <row r="39" spans="1:5">
-      <c r="B39" s="13"/>
-      <c r="D39" s="13"/>
+      <c r="A39" s="3"/>
+      <c r="D39" s="3"/>
     </row>
     <row r="40" spans="1:5">
-      <c r="B40" s="13"/>
-      <c r="D40" s="13"/>
+      <c r="A40" s="3"/>
+      <c r="D40" s="3"/>
     </row>
     <row r="41" spans="1:5">
-      <c r="B41" s="13"/>
-      <c r="D41" s="13"/>
+      <c r="A41" s="3"/>
+      <c r="D41" s="3"/>
     </row>
     <row r="42" spans="1:5">
-      <c r="B42" s="13"/>
-      <c r="D42" s="13"/>
+      <c r="A42" s="3"/>
+      <c r="D42" s="3"/>
     </row>
     <row r="43" spans="1:5">
-      <c r="B43" s="13"/>
-      <c r="D43" s="13"/>
+      <c r="A43" s="3"/>
+      <c r="D43" s="3"/>
     </row>
     <row r="44" spans="1:5">
-      <c r="B44" s="13"/>
-      <c r="D44" s="13"/>
+      <c r="A44" s="3"/>
+      <c r="D44" s="3"/>
     </row>
     <row r="45" spans="1:5">
-      <c r="B45" s="13"/>
-      <c r="D45" s="13"/>
+      <c r="A45" s="3"/>
+      <c r="D45" s="3"/>
     </row>
     <row r="46" spans="1:5">
-      <c r="B46" s="13"/>
-      <c r="D46" s="13"/>
+      <c r="A46" s="3"/>
+      <c r="D46" s="3"/>
     </row>
     <row r="47" spans="1:5">
-      <c r="B47" s="13"/>
-      <c r="D47" s="13"/>
+      <c r="A47" s="3"/>
+      <c r="D47" s="3"/>
     </row>
     <row r="48" spans="1:5">
-      <c r="B48" s="13"/>
-      <c r="D48" s="13"/>
-    </row>
-    <row r="49" spans="2:4">
-      <c r="B49" s="13"/>
-      <c r="D49" s="13"/>
-    </row>
-    <row r="50" spans="2:4">
-      <c r="B50" s="13"/>
-      <c r="D50" s="13"/>
-    </row>
-    <row r="51" spans="2:4">
-      <c r="B51" s="13"/>
-      <c r="D51" s="13"/>
-    </row>
-    <row r="52" spans="2:4">
-      <c r="B52" s="13"/>
-      <c r="D52" s="13"/>
-    </row>
-    <row r="61" s="2" customFormat="1" spans="2:4">
-      <c r="B61" s="3"/>
-      <c r="C61" s="3"/>
-    </row>
-    <row r="64" spans="2:4">
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-    </row>
-    <row r="65" spans="2:3">
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-    </row>
-    <row r="66" spans="2:3">
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
+      <c r="A48" s="3"/>
+      <c r="D48" s="3"/>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="3"/>
+      <c r="D49" s="3"/>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="3"/>
+      <c r="D50" s="3"/>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="3"/>
+      <c r="D51" s="3"/>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="B52" s="12"/>
+      <c r="D52" s="12"/>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="B53" s="12"/>
+      <c r="D53" s="12"/>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="B54" s="12"/>
+      <c r="D54" s="12"/>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="B55" s="12"/>
+      <c r="D55" s="12"/>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="B56" s="12"/>
+      <c r="D56" s="12"/>
+    </row>
+    <row r="65" s="2" customFormat="1" spans="2:3">
+      <c r="B65" s="3"/>
+      <c r="C65" s="3"/>
+    </row>
+    <row r="68" spans="2:3">
+      <c r="B68" s="13"/>
+      <c r="C68" s="13"/>
+    </row>
+    <row r="69" spans="2:3">
+      <c r="B69" s="13"/>
+      <c r="C69" s="13"/>
+    </row>
+    <row r="70" spans="2:3">
+      <c r="B70" s="13"/>
+      <c r="C70" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tools/i18n/FrameworkI18n.xlsx
+++ b/tools/i18n/FrameworkI18n.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="120">
   <si>
     <t>key</t>
   </si>
@@ -365,6 +365,33 @@
   </si>
   <si>
     <t>Approval Number: Xin Chang Chu Shen [2017] No. 4343 Publication Number: ISBN 978-7-7979-7728-9 Publisher: Fuzhou 169 Company</t>
+  </si>
+  <si>
+    <t>MODIFY_NICKNAME</t>
+  </si>
+  <si>
+    <t>修改昵称</t>
+  </si>
+  <si>
+    <t>Change Nickname</t>
+  </si>
+  <si>
+    <t>OLD_NICKNAME</t>
+  </si>
+  <si>
+    <t>原昵称</t>
+  </si>
+  <si>
+    <t>Current Nickname</t>
+  </si>
+  <si>
+    <t>NEW_NICKNAME</t>
+  </si>
+  <si>
+    <t>新昵称</t>
+  </si>
+  <si>
+    <t>New Nickname</t>
   </si>
 </sst>
 </file>
@@ -377,7 +404,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -400,6 +427,12 @@
     <font>
       <b/>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -859,158 +892,158 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1033,7 +1066,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -1420,8 +1453,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:E70"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
+  <dimension ref="A1:E67"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.25" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="26.5" style="2" customWidth="1"/>
     <col min="2" max="2" width="47.825" style="3" customWidth="1"/>
@@ -1429,7 +1462,7 @@
     <col min="4" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" spans="1:5">
+    <row r="1" spans="1:5">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1442,7 +1475,7 @@
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
     </row>
-    <row r="2" ht="17.25" spans="1:5">
+    <row r="2" spans="1:5">
       <c r="A2" s="6" t="s">
         <v>3</v>
       </c>
@@ -1468,7 +1501,7 @@
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
     </row>
-    <row r="4" ht="17.25" spans="1:5">
+    <row r="4" spans="1:5">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
@@ -1481,7 +1514,7 @@
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
     </row>
-    <row r="5" ht="17.25" spans="1:5">
+    <row r="5" spans="1:5">
       <c r="A5" s="6" t="s">
         <v>12</v>
       </c>
@@ -1494,7 +1527,7 @@
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
     </row>
-    <row r="6" ht="17.25" spans="1:5">
+    <row r="6" spans="1:5">
       <c r="A6" s="6" t="s">
         <v>15</v>
       </c>
@@ -1507,7 +1540,7 @@
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
     </row>
-    <row r="7" ht="17.25" spans="1:5">
+    <row r="7" spans="1:5">
       <c r="A7" s="6" t="s">
         <v>18</v>
       </c>
@@ -1520,7 +1553,7 @@
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
     </row>
-    <row r="8" ht="17.25" spans="1:5">
+    <row r="8" spans="1:5">
       <c r="A8" s="6" t="s">
         <v>21</v>
       </c>
@@ -1533,7 +1566,7 @@
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
     </row>
-    <row r="9" ht="17.25" spans="1:5">
+    <row r="9" spans="1:5">
       <c r="A9" s="6" t="s">
         <v>24</v>
       </c>
@@ -1546,7 +1579,7 @@
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
     </row>
-    <row r="10" ht="17.25" spans="1:5">
+    <row r="10" spans="1:5">
       <c r="A10" s="6" t="s">
         <v>27</v>
       </c>
@@ -1559,7 +1592,7 @@
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
     </row>
-    <row r="11" ht="17.25" spans="1:5">
+    <row r="11" spans="1:5">
       <c r="A11" s="8" t="s">
         <v>30</v>
       </c>
@@ -1572,7 +1605,7 @@
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
     </row>
-    <row r="12" ht="17.25" spans="1:5">
+    <row r="12" spans="1:5">
       <c r="A12" s="8" t="s">
         <v>33</v>
       </c>
@@ -1585,7 +1618,7 @@
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
     </row>
-    <row r="13" ht="17.25" spans="1:5">
+    <row r="13" spans="1:5">
       <c r="A13" s="8" t="s">
         <v>36</v>
       </c>
@@ -1598,7 +1631,7 @@
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
     </row>
-    <row r="14" ht="17.25" spans="1:5">
+    <row r="14" spans="1:5">
       <c r="A14" s="8" t="s">
         <v>39</v>
       </c>
@@ -1611,7 +1644,7 @@
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
     </row>
-    <row r="15" ht="17.25" spans="1:5">
+    <row r="15" spans="1:5">
       <c r="A15" s="8" t="s">
         <v>42</v>
       </c>
@@ -1624,7 +1657,7 @@
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
     </row>
-    <row r="16" ht="17.25" spans="1:5">
+    <row r="16" spans="1:5">
       <c r="A16" s="8" t="s">
         <v>45</v>
       </c>
@@ -1637,7 +1670,7 @@
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
     </row>
-    <row r="17" ht="17.25" spans="1:5">
+    <row r="17" spans="1:5">
       <c r="A17" s="8" t="s">
         <v>48</v>
       </c>
@@ -1650,7 +1683,7 @@
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
     </row>
-    <row r="18" ht="17.25" spans="1:5">
+    <row r="18" spans="1:5">
       <c r="A18" s="8" t="s">
         <v>51</v>
       </c>
@@ -1663,7 +1696,7 @@
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
     </row>
-    <row r="19" ht="17.25" spans="1:5">
+    <row r="19" spans="1:5">
       <c r="A19" s="8" t="s">
         <v>54</v>
       </c>
@@ -1676,7 +1709,7 @@
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
     </row>
-    <row r="20" ht="17.25" spans="1:5">
+    <row r="20" spans="1:5">
       <c r="A20" s="8" t="s">
         <v>57</v>
       </c>
@@ -1689,7 +1722,7 @@
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
     </row>
-    <row r="21" ht="17.25" spans="1:5">
+    <row r="21" spans="1:5">
       <c r="A21" s="8" t="s">
         <v>60</v>
       </c>
@@ -1702,7 +1735,7 @@
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
     </row>
-    <row r="22" ht="17.25" spans="1:5">
+    <row r="22" spans="1:5">
       <c r="A22" s="8" t="s">
         <v>63</v>
       </c>
@@ -1715,7 +1748,7 @@
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
     </row>
-    <row r="23" ht="17.25" spans="1:5">
+    <row r="23" spans="1:5">
       <c r="A23" s="8" t="s">
         <v>66</v>
       </c>
@@ -1728,7 +1761,7 @@
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
     </row>
-    <row r="24" ht="17.25" spans="1:5">
+    <row r="24" spans="1:5">
       <c r="A24" s="8" t="s">
         <v>69</v>
       </c>
@@ -1741,7 +1774,7 @@
       <c r="D24" s="6"/>
       <c r="E24" s="6"/>
     </row>
-    <row r="25" ht="17.25" spans="1:5">
+    <row r="25" spans="1:5">
       <c r="A25" s="8" t="s">
         <v>72</v>
       </c>
@@ -1754,7 +1787,7 @@
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
     </row>
-    <row r="26" ht="17.25" spans="1:5">
+    <row r="26" spans="1:5">
       <c r="A26" s="9" t="s">
         <v>75</v>
       </c>
@@ -1780,7 +1813,7 @@
       <c r="D27" s="10"/>
       <c r="E27" s="4"/>
     </row>
-    <row r="28" ht="17.25" spans="1:5">
+    <row r="28" spans="1:5">
       <c r="A28" s="9" t="s">
         <v>81</v>
       </c>
@@ -1793,7 +1826,7 @@
       <c r="D28" s="11"/>
       <c r="E28" s="4"/>
     </row>
-    <row r="29" ht="17.25" spans="1:5">
+    <row r="29" spans="1:5">
       <c r="A29" s="9" t="s">
         <v>84</v>
       </c>
@@ -1806,7 +1839,7 @@
       <c r="D29" s="11"/>
       <c r="E29" s="4"/>
     </row>
-    <row r="30" ht="17.25" spans="1:5">
+    <row r="30" spans="1:5">
       <c r="A30" s="9" t="s">
         <v>87</v>
       </c>
@@ -1819,7 +1852,7 @@
       <c r="D30" s="11"/>
       <c r="E30" s="4"/>
     </row>
-    <row r="31" ht="17.25" spans="1:5">
+    <row r="31" spans="1:5">
       <c r="A31" s="9" t="s">
         <v>90</v>
       </c>
@@ -1832,7 +1865,7 @@
       <c r="D31" s="11"/>
       <c r="E31" s="4"/>
     </row>
-    <row r="32" customFormat="1" ht="17.25" spans="1:5">
+    <row r="32" spans="1:5">
       <c r="A32" s="9" t="s">
         <v>93</v>
       </c>
@@ -1845,7 +1878,7 @@
       <c r="D32" s="11"/>
       <c r="E32" s="4"/>
     </row>
-    <row r="33" s="1" customFormat="1" ht="17.25" spans="1:5">
+    <row r="33" s="1" customFormat="1" spans="1:5">
       <c r="A33" s="9" t="s">
         <v>96</v>
       </c>
@@ -1856,81 +1889,112 @@
         <v>98</v>
       </c>
     </row>
-    <row r="34" s="1" customFormat="1" ht="17.25" spans="1:5">
-      <c r="A34" s="9" t="s">
+    <row r="34" s="1" customFormat="1" spans="1:5">
+      <c r="A34" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="C34" s="8" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" ht="17.25" spans="1:5">
-      <c r="A35" s="9" t="s">
+    <row r="35" s="1" customFormat="1" spans="1:5">
+      <c r="A35" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="C35" s="8" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="36" s="2" customFormat="1" ht="17.25" spans="1:5">
-      <c r="A36" s="3" t="s">
+    <row r="36" s="2" customFormat="1" ht="51.75" spans="1:5">
+      <c r="A36" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="8" t="s">
         <v>107</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="4"/>
     </row>
-    <row r="37" ht="17.25" spans="1:5">
-      <c r="A37" s="3" t="s">
+    <row r="37" ht="51.75" spans="1:5">
+      <c r="A37" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="8" t="s">
         <v>110</v>
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="4"/>
     </row>
-    <row r="38" ht="17.25" spans="1:5">
-      <c r="A38" s="3"/>
+    <row r="38" spans="1:5">
+      <c r="A38" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>113</v>
+      </c>
       <c r="D38" s="3"/>
-      <c r="E38" s="4"/>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="3"/>
+      <c r="A39" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>116</v>
+      </c>
       <c r="D39" s="3"/>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="3"/>
+      <c r="A40" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>119</v>
+      </c>
       <c r="D40" s="3"/>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="3"/>
+      <c r="A41" s="8"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="8"/>
       <c r="D41" s="3"/>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="3"/>
+      <c r="A42" s="8"/>
+      <c r="B42" s="8"/>
+      <c r="C42" s="8"/>
       <c r="D42" s="3"/>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="3"/>
+      <c r="A43" s="8"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
       <c r="D43" s="3"/>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="3"/>
+      <c r="A44" s="8"/>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
       <c r="D44" s="3"/>
     </row>
     <row r="45" spans="1:5">
@@ -1949,53 +2013,41 @@
       <c r="A48" s="3"/>
       <c r="D48" s="3"/>
     </row>
-    <row r="49" spans="1:4">
-      <c r="A49" s="3"/>
-      <c r="D49" s="3"/>
-    </row>
-    <row r="50" spans="1:4">
-      <c r="A50" s="3"/>
-      <c r="D50" s="3"/>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" s="3"/>
-      <c r="D51" s="3"/>
-    </row>
-    <row r="52" spans="1:4">
+    <row r="49" spans="2:4">
+      <c r="B49" s="12"/>
+      <c r="D49" s="12"/>
+    </row>
+    <row r="50" spans="2:4">
+      <c r="B50" s="12"/>
+      <c r="D50" s="12"/>
+    </row>
+    <row r="51" spans="2:4">
+      <c r="B51" s="12"/>
+      <c r="D51" s="12"/>
+    </row>
+    <row r="52" spans="2:4">
       <c r="B52" s="12"/>
       <c r="D52" s="12"/>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="2:4">
       <c r="B53" s="12"/>
       <c r="D53" s="12"/>
     </row>
-    <row r="54" spans="1:4">
-      <c r="B54" s="12"/>
-      <c r="D54" s="12"/>
-    </row>
-    <row r="55" spans="1:4">
-      <c r="B55" s="12"/>
-      <c r="D55" s="12"/>
-    </row>
-    <row r="56" spans="1:4">
-      <c r="B56" s="12"/>
-      <c r="D56" s="12"/>
-    </row>
-    <row r="65" s="2" customFormat="1" spans="2:3">
-      <c r="B65" s="3"/>
-      <c r="C65" s="3"/>
-    </row>
-    <row r="68" spans="2:3">
-      <c r="B68" s="13"/>
-      <c r="C68" s="13"/>
-    </row>
-    <row r="69" spans="2:3">
-      <c r="B69" s="13"/>
-      <c r="C69" s="13"/>
-    </row>
-    <row r="70" spans="2:3">
-      <c r="B70" s="13"/>
-      <c r="C70" s="13"/>
+    <row r="62" s="2" customFormat="1" spans="2:4">
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+    </row>
+    <row r="65" spans="2:3">
+      <c r="B65" s="13"/>
+      <c r="C65" s="13"/>
+    </row>
+    <row r="66" spans="2:3">
+      <c r="B66" s="13"/>
+      <c r="C66" s="13"/>
+    </row>
+    <row r="67" spans="2:3">
+      <c r="B67" s="13"/>
+      <c r="C67" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tools/i18n/FrameworkI18n.xlsx
+++ b/tools/i18n/FrameworkI18n.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="135">
   <si>
     <t>key</t>
   </si>
@@ -392,6 +392,51 @@
   </si>
   <si>
     <t>New Nickname</t>
+  </si>
+  <si>
+    <t>HOUR</t>
+  </si>
+  <si>
+    <t>时</t>
+  </si>
+  <si>
+    <t>Hour</t>
+  </si>
+  <si>
+    <t>MINUTE</t>
+  </si>
+  <si>
+    <t>分</t>
+  </si>
+  <si>
+    <t>Minute</t>
+  </si>
+  <si>
+    <t>SECOND</t>
+  </si>
+  <si>
+    <t>秒</t>
+  </si>
+  <si>
+    <t>Second</t>
+  </si>
+  <si>
+    <t>HOUR_S</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>MINUTE_S</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>SECOND_S</t>
+  </si>
+  <si>
+    <t>S</t>
   </si>
 </sst>
 </file>
@@ -1043,10 +1088,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1066,8 +1109,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
@@ -1453,17 +1496,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.25" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="26.5" style="2" customWidth="1"/>
-    <col min="2" max="2" width="47.825" style="3" customWidth="1"/>
-    <col min="3" max="3" width="93.15" style="3" customWidth="1"/>
+    <col min="2" max="2" width="47.825" style="4" customWidth="1"/>
+    <col min="3" max="3" width="93.15" style="4" customWidth="1"/>
     <col min="4" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
@@ -1472,8 +1515,6 @@
       <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="6" t="s">
@@ -1495,7 +1536,7 @@
       <c r="B3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="6"/>
@@ -1811,7 +1852,6 @@
         <v>80</v>
       </c>
       <c r="D27" s="10"/>
-      <c r="E27" s="4"/>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="9" t="s">
@@ -1824,7 +1864,6 @@
         <v>83</v>
       </c>
       <c r="D28" s="11"/>
-      <c r="E28" s="4"/>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="9" t="s">
@@ -1837,7 +1876,6 @@
         <v>86</v>
       </c>
       <c r="D29" s="11"/>
-      <c r="E29" s="4"/>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="9" t="s">
@@ -1850,7 +1888,6 @@
         <v>89</v>
       </c>
       <c r="D30" s="11"/>
-      <c r="E30" s="4"/>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="9" t="s">
@@ -1863,7 +1900,6 @@
         <v>92</v>
       </c>
       <c r="D31" s="11"/>
-      <c r="E31" s="4"/>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="9" t="s">
@@ -1876,9 +1912,8 @@
         <v>95</v>
       </c>
       <c r="D32" s="11"/>
-      <c r="E32" s="4"/>
-    </row>
-    <row r="33" s="1" customFormat="1" spans="1:5">
+    </row>
+    <row r="33" s="1" customFormat="1" spans="1:4">
       <c r="A33" s="9" t="s">
         <v>96</v>
       </c>
@@ -1889,7 +1924,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="34" s="1" customFormat="1" spans="1:5">
+    <row r="34" s="1" customFormat="1" spans="1:4">
       <c r="A34" s="8" t="s">
         <v>99</v>
       </c>
@@ -1900,142 +1935,183 @@
         <v>101</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" spans="1:5">
-      <c r="A35" s="8" t="s">
+    <row r="35" s="1" customFormat="1" spans="1:4">
+      <c r="A35" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="12" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="36" s="2" customFormat="1" ht="51.75" spans="1:5">
-      <c r="A36" s="8" t="s">
+    <row r="36" s="2" customFormat="1" ht="51.75" spans="1:4">
+      <c r="A36" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C36" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="D36" s="3"/>
-      <c r="E36" s="4"/>
-    </row>
-    <row r="37" ht="51.75" spans="1:5">
-      <c r="A37" s="8" t="s">
+      <c r="D36" s="4"/>
+    </row>
+    <row r="37" ht="51.75" spans="1:4">
+      <c r="A37" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="C37" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D37" s="3"/>
-      <c r="E37" s="4"/>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="8" t="s">
+      <c r="D37" s="4"/>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="B38" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="C38" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="D38" s="3"/>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="8" t="s">
+      <c r="D38" s="4"/>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="B39" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C39" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="D39" s="3"/>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="8" t="s">
+      <c r="D39" s="4"/>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="B40" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="C40" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="D40" s="3"/>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="8"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="3"/>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="8"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="3"/>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="8"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="3"/>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="8"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="8"/>
-      <c r="D44" s="3"/>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3"/>
-      <c r="D45" s="3"/>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3"/>
-      <c r="D46" s="3"/>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3"/>
-      <c r="D47" s="3"/>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3"/>
-      <c r="D48" s="3"/>
-    </row>
-    <row r="49" spans="2:4">
+      <c r="D40" s="4"/>
+    </row>
+    <row r="41" s="3" customFormat="1" spans="1:4">
+      <c r="A41" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="42" s="3" customFormat="1" spans="1:4">
+      <c r="A42" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="43" s="3" customFormat="1" spans="1:4">
+      <c r="A43" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D44" s="4"/>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="D45" s="4"/>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="D46" s="4"/>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="12"/>
+      <c r="B47" s="12"/>
+      <c r="C47" s="12"/>
+      <c r="D47" s="4"/>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="12"/>
+      <c r="B48" s="12"/>
+      <c r="C48" s="12"/>
+      <c r="D48" s="11"/>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="12"/>
       <c r="B49" s="12"/>
-      <c r="D49" s="12"/>
-    </row>
-    <row r="50" spans="2:4">
-      <c r="B50" s="12"/>
-      <c r="D50" s="12"/>
-    </row>
-    <row r="51" spans="2:4">
-      <c r="B51" s="12"/>
-      <c r="D51" s="12"/>
-    </row>
-    <row r="52" spans="2:4">
-      <c r="B52" s="12"/>
-      <c r="D52" s="12"/>
-    </row>
-    <row r="53" spans="2:4">
-      <c r="B53" s="12"/>
-      <c r="D53" s="12"/>
-    </row>
-    <row r="62" s="2" customFormat="1" spans="2:4">
-      <c r="B62" s="3"/>
-      <c r="C62" s="3"/>
+      <c r="C49" s="12"/>
+      <c r="D49" s="11"/>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="B50" s="11"/>
+      <c r="D50" s="11"/>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="B51" s="11"/>
+      <c r="D51" s="11"/>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="B52" s="11"/>
+      <c r="D52" s="11"/>
+    </row>
+    <row r="61" s="2" customFormat="1" spans="1:4">
+      <c r="B61" s="4"/>
+      <c r="C61" s="4"/>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="B64" s="13"/>
+      <c r="C64" s="13"/>
     </row>
     <row r="65" spans="2:3">
       <c r="B65" s="13"/>
@@ -2044,10 +2120,6 @@
     <row r="66" spans="2:3">
       <c r="B66" s="13"/>
       <c r="C66" s="13"/>
-    </row>
-    <row r="67" spans="2:3">
-      <c r="B67" s="13"/>
-      <c r="C67" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
